--- a/backend/data/financials_by_company/1027.HK.xlsx
+++ b/backend/data/financials_by_company/1027.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,575 +664,678 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization In Income Statement</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Depreciation Income Statement</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Research And Development</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-382603.399221</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.18546</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24777000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2063000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2063000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5256000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>322584000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22714000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>17458000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-2974000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>4102000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1128000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>12559396.600779</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>338520000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>412550000</v>
+        <v>298731000</v>
       </c>
       <c r="T2" t="n">
-        <v>412550000</v>
+        <v>298731000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0264</v>
+        <v>-0.4276</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0264</v>
-      </c>
-      <c r="W2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10879000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2477000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13356000</v>
-      </c>
+        <v>-0.4276</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-40000</v>
+        <v>-14332000</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>-2974000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4102000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1128000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14744000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>15936000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-36209000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>52562000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15890000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>36672000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>30680000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>322584000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>353264000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>353264000</v>
-      </c>
+      <c r="AH2" t="n">
+        <v>3534000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>8504000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7537000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-76400</v>
+        <v>38600</v>
       </c>
       <c r="C3" t="n">
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-84202000</v>
+        <v>-15536000</v>
       </c>
       <c r="E3" t="n">
-        <v>-382000</v>
+        <v>193000</v>
       </c>
       <c r="F3" t="n">
-        <v>-382000</v>
+        <v>193000</v>
       </c>
       <c r="G3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="H3" t="n">
-        <v>5076000</v>
+        <v>5344000</v>
       </c>
       <c r="I3" t="n">
-        <v>273075000</v>
+        <v>318582000</v>
       </c>
       <c r="J3" t="n">
-        <v>-84584000</v>
+        <v>-15343000</v>
       </c>
       <c r="K3" t="n">
-        <v>-89660000</v>
+        <v>-20687000</v>
       </c>
       <c r="L3" t="n">
-        <v>-688000</v>
+        <v>1260000</v>
       </c>
       <c r="M3" t="n">
-        <v>3045000</v>
+        <v>3954000</v>
       </c>
       <c r="N3" t="n">
-        <v>2357000</v>
+        <v>5214000</v>
       </c>
       <c r="O3" t="n">
-        <v>-92445400</v>
+        <v>-29587400</v>
       </c>
       <c r="P3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="Q3" t="n">
-        <v>387757000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10000</v>
-      </c>
+        <v>391442000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>412550000</v>
+        <v>367188000</v>
       </c>
       <c r="T3" t="n">
-        <v>412550000</v>
+        <v>367188000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.22</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.22</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="X3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-92751000</v>
+        <v>-29433000</v>
       </c>
       <c r="AC3" t="n">
-        <v>46000</v>
+        <v>4792000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-92705000</v>
+        <v>-24641000</v>
       </c>
       <c r="AE3" t="n">
-        <v>116000</v>
+        <v>530000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+        <v>5056000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-5056000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>9254000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>-688000</v>
+        <v>1260000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3045000</v>
+        <v>3954000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2357000</v>
+        <v>5214000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-93290000</v>
+        <v>-37494000</v>
       </c>
       <c r="AO3" t="n">
-        <v>114682000</v>
+        <v>72860000</v>
       </c>
       <c r="AP3" t="n">
-        <v>68696000</v>
+        <v>9254000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>47012000</v>
+        <v>65825000</v>
       </c>
       <c r="AR3" t="n">
-        <v>14450000</v>
+        <v>22050000</v>
       </c>
       <c r="AS3" t="n">
-        <v>32562000</v>
+        <v>43775000</v>
       </c>
       <c r="AT3" t="n">
-        <v>21392000</v>
+        <v>35366000</v>
       </c>
       <c r="AU3" t="n">
-        <v>273075000</v>
+        <v>318582000</v>
       </c>
       <c r="AV3" t="n">
-        <v>294467000</v>
+        <v>353948000</v>
       </c>
       <c r="AW3" t="n">
-        <v>294467000</v>
-      </c>
+        <v>353948000</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>38600</v>
+        <v>-76400</v>
       </c>
       <c r="C4" t="n">
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-15536000</v>
+        <v>-84202000</v>
       </c>
       <c r="E4" t="n">
-        <v>193000</v>
+        <v>-382000</v>
       </c>
       <c r="F4" t="n">
-        <v>193000</v>
+        <v>-382000</v>
       </c>
       <c r="G4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="H4" t="n">
-        <v>5344000</v>
+        <v>5076000</v>
       </c>
       <c r="I4" t="n">
-        <v>318582000</v>
+        <v>273075000</v>
       </c>
       <c r="J4" t="n">
-        <v>-15343000</v>
+        <v>-84584000</v>
       </c>
       <c r="K4" t="n">
-        <v>-20687000</v>
+        <v>-89660000</v>
       </c>
       <c r="L4" t="n">
-        <v>1260000</v>
+        <v>-688000</v>
       </c>
       <c r="M4" t="n">
-        <v>3954000</v>
+        <v>3045000</v>
       </c>
       <c r="N4" t="n">
-        <v>5214000</v>
+        <v>2357000</v>
       </c>
       <c r="O4" t="n">
-        <v>-29587400</v>
+        <v>-92445400</v>
       </c>
       <c r="P4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="Q4" t="n">
-        <v>391442000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>387757000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10000</v>
+      </c>
       <c r="S4" t="n">
-        <v>367188000</v>
+        <v>412550000</v>
       </c>
       <c r="T4" t="n">
-        <v>367188000</v>
+        <v>412550000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="W4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="X4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-29433000</v>
+        <v>-92751000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4792000</v>
+        <v>46000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-24641000</v>
+        <v>-92705000</v>
       </c>
       <c r="AE4" t="n">
-        <v>530000</v>
+        <v>116000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5056000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-5056000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>9254000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>1260000</v>
+        <v>-688000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3954000</v>
+        <v>3045000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5214000</v>
+        <v>2357000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-37494000</v>
+        <v>-93290000</v>
       </c>
       <c r="AO4" t="n">
-        <v>72860000</v>
+        <v>114682000</v>
       </c>
       <c r="AP4" t="n">
-        <v>9254000</v>
+        <v>68696000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>65825000</v>
+        <v>47012000</v>
       </c>
       <c r="AR4" t="n">
-        <v>22050000</v>
+        <v>14450000</v>
       </c>
       <c r="AS4" t="n">
-        <v>43775000</v>
+        <v>32562000</v>
       </c>
       <c r="AT4" t="n">
-        <v>35366000</v>
+        <v>21392000</v>
       </c>
       <c r="AU4" t="n">
-        <v>318582000</v>
+        <v>273075000</v>
       </c>
       <c r="AV4" t="n">
-        <v>353948000</v>
+        <v>294467000</v>
       </c>
       <c r="AW4" t="n">
-        <v>353948000</v>
-      </c>
+        <v>294467000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-4809800</v>
+        <v>-382603.399221</v>
       </c>
       <c r="C5" t="n">
+        <v>0.18546</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24777000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2063000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2063000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5256000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>322584000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22714000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17458000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2974000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4102000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1128000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12559396.600779</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>338520000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>412550000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>412550000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="W5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10879000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2477000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13356000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>-2974000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4102000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1128000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14744000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15936000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-36209000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>35647000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15890000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>19757000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>30680000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>322584000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>353264000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>353264000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3539000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3539000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13376000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-422400</v>
+      </c>
+      <c r="C6" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" t="n">
-        <v>-96400000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-18379000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-24049000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6542000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>279154000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-114779000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-121321000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-3095000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3861000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>766000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-102819800</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>387489000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>298731000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>298731000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.4276</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.4276</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-127729000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2547000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-125182000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-14332000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-25245000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>3534000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8504000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7537000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-3095000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3861000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>766000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-81435000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>108335000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>110973000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>31133000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>79840000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>26900000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>279154000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>306054000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>306054000</v>
+      <c r="D6" t="n">
+        <v>2631000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2112000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2112000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5345000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>256065000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>519000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4826000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2157000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3609000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1452000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-8426400</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>277197000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-10116000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1681000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-8435000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>-10108000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>10108000</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>-2157000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3609000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1452000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-677000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>21132000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-32118000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>36528000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13585000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>22943000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>20455000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>256065000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>276520000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>276520000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3602000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3602000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13197000</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,174 +1656,92 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>412550000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>412550000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>77325000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>81470000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>332919000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>193396000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>251449000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5947000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-54867000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>177394000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10818000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10818000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>148128000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>148128000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>81470000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>81470000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>56249000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2186000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2665000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>51398000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>399577000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>58053000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>58053000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-73565000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>131618000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>364000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>6710000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>446000</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>33047000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>86521000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12050000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>341524000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>22843000</v>
-      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>30321000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>135648000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>12150000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6291000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>117207000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15874000</v>
-      </c>
+        <v>33150000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>12110000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>114156000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-41837000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>155993000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10572000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6427000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4145000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4145000</v>
-      </c>
+        <v>8132000</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>412550000</v>
@@ -1729,40 +1750,40 @@
         <v>412550000</v>
       </c>
       <c r="D3" t="n">
-        <v>60296000</v>
+        <v>51529000</v>
       </c>
       <c r="E3" t="n">
-        <v>73390000</v>
+        <v>68100000</v>
       </c>
       <c r="F3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="G3" t="n">
-        <v>312988000</v>
+        <v>399912000</v>
       </c>
       <c r="H3" t="n">
-        <v>173113000</v>
+        <v>260986000</v>
       </c>
       <c r="I3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="J3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="K3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="L3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="M3" t="n">
-        <v>239598000</v>
+        <v>331812000</v>
       </c>
       <c r="N3" t="n">
-        <v>5960000</v>
+        <v>11238000</v>
       </c>
       <c r="O3" t="n">
-        <v>-65759000</v>
+        <v>21714000</v>
       </c>
       <c r="P3" t="n">
         <v>177394000</v>
@@ -1774,126 +1795,136 @@
         <v>10818000</v>
       </c>
       <c r="S3" t="n">
-        <v>142462000</v>
+        <v>136628000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>315000</v>
       </c>
       <c r="V3" t="n">
-        <v>142462000</v>
+        <v>136313000</v>
       </c>
       <c r="W3" t="n">
-        <v>73390000</v>
+        <v>68100000</v>
       </c>
       <c r="X3" t="n">
-        <v>73390000</v>
+        <v>68100000</v>
       </c>
       <c r="Y3" t="n">
-        <v>47143000</v>
+        <v>62486000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1791000</v>
+        <v>563000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2102000</v>
+        <v>2468000</v>
       </c>
       <c r="AB3" t="n">
-        <v>45041000</v>
+        <v>59455000</v>
       </c>
       <c r="AC3" t="n">
-        <v>382060000</v>
+        <v>468440000</v>
       </c>
       <c r="AD3" t="n">
-        <v>66485000</v>
+        <v>71141000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>6710000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5000000</v>
+      </c>
       <c r="AG3" t="n">
         <v>5000000</v>
       </c>
       <c r="AH3" t="n">
         <v>5000000</v>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>61485000</v>
+        <v>59431000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-69150000</v>
+        <v>-66190000</v>
       </c>
       <c r="AM3" t="n">
-        <v>130635000</v>
+        <v>125621000</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>59431000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>31527000</v>
+        <v>25977000</v>
       </c>
       <c r="AQ3" t="n">
         <v>86521000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12587000</v>
+        <v>13123000</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>315575000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>17673000</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
+        <v>397299000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>29902000</v>
+      </c>
       <c r="AW3" t="n">
-        <v>115366000</v>
+        <v>132269000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1063000</v>
+        <v>12878000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1618000</v>
+        <v>3051000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>112685000</v>
+        <v>116340000</v>
       </c>
       <c r="BA3" t="n">
-        <v>68738000</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>76436000</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5919000</v>
+      </c>
       <c r="BC3" t="n">
-        <v>92925000</v>
+        <v>148571000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-77807000</v>
+        <v>-3353000</v>
       </c>
       <c r="BE3" t="n">
-        <v>170732000</v>
+        <v>151924000</v>
       </c>
       <c r="BF3" t="n">
-        <v>20873000</v>
+        <v>40023000</v>
       </c>
       <c r="BG3" t="n">
-        <v>7779000</v>
+        <v>23452000</v>
       </c>
       <c r="BH3" t="n">
-        <v>13094000</v>
+        <v>16571000</v>
       </c>
       <c r="BI3" t="n">
-        <v>13094000</v>
+        <v>16571000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>412550000</v>
@@ -1902,40 +1933,40 @@
         <v>412550000</v>
       </c>
       <c r="D4" t="n">
-        <v>51529000</v>
+        <v>60296000</v>
       </c>
       <c r="E4" t="n">
-        <v>68100000</v>
+        <v>73390000</v>
       </c>
       <c r="F4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="G4" t="n">
-        <v>399912000</v>
+        <v>312988000</v>
       </c>
       <c r="H4" t="n">
-        <v>260986000</v>
+        <v>173113000</v>
       </c>
       <c r="I4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="J4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="K4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="L4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="M4" t="n">
-        <v>331812000</v>
+        <v>239598000</v>
       </c>
       <c r="N4" t="n">
-        <v>11238000</v>
+        <v>5960000</v>
       </c>
       <c r="O4" t="n">
-        <v>21714000</v>
+        <v>-65759000</v>
       </c>
       <c r="P4" t="n">
         <v>177394000</v>
@@ -1947,306 +1978,455 @@
         <v>10818000</v>
       </c>
       <c r="S4" t="n">
-        <v>136628000</v>
+        <v>142462000</v>
       </c>
       <c r="T4" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>315000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>136313000</v>
+        <v>142462000</v>
       </c>
       <c r="W4" t="n">
-        <v>68100000</v>
+        <v>73390000</v>
       </c>
       <c r="X4" t="n">
-        <v>68100000</v>
+        <v>73390000</v>
       </c>
       <c r="Y4" t="n">
-        <v>62486000</v>
+        <v>47143000</v>
       </c>
       <c r="Z4" t="n">
-        <v>563000</v>
+        <v>1791000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2468000</v>
+        <v>2102000</v>
       </c>
       <c r="AB4" t="n">
-        <v>59455000</v>
+        <v>45041000</v>
       </c>
       <c r="AC4" t="n">
-        <v>468440000</v>
+        <v>382060000</v>
       </c>
       <c r="AD4" t="n">
-        <v>71141000</v>
+        <v>66485000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6710000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>5000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
         <v>5000000</v>
       </c>
       <c r="AH4" t="n">
         <v>5000000</v>
       </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>59431000</v>
+        <v>61485000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-66190000</v>
+        <v>-69150000</v>
       </c>
       <c r="AM4" t="n">
-        <v>125621000</v>
+        <v>130635000</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
-      <c r="AO4" t="n">
-        <v>59431000</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>25977000</v>
+        <v>31527000</v>
       </c>
       <c r="AQ4" t="n">
         <v>86521000</v>
       </c>
       <c r="AR4" t="n">
-        <v>13123000</v>
+        <v>12587000</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>397299000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>29902000</v>
-      </c>
+        <v>315575000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>17673000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>132269000</v>
+        <v>115366000</v>
       </c>
       <c r="AX4" t="n">
-        <v>12878000</v>
+        <v>1063000</v>
       </c>
       <c r="AY4" t="n">
-        <v>3051000</v>
+        <v>1618000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>116340000</v>
+        <v>112685000</v>
       </c>
       <c r="BA4" t="n">
-        <v>76436000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5919000</v>
-      </c>
+        <v>68738000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>148571000</v>
+        <v>92925000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-3353000</v>
+        <v>-77807000</v>
       </c>
       <c r="BE4" t="n">
-        <v>151924000</v>
+        <v>170732000</v>
       </c>
       <c r="BF4" t="n">
-        <v>40023000</v>
+        <v>20873000</v>
       </c>
       <c r="BG4" t="n">
-        <v>23452000</v>
+        <v>7779000</v>
       </c>
       <c r="BH4" t="n">
-        <v>16571000</v>
+        <v>13094000</v>
       </c>
       <c r="BI4" t="n">
-        <v>16571000</v>
+        <v>13094000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>302880000</v>
+        <v>412550000</v>
       </c>
       <c r="C5" t="n">
-        <v>302880000</v>
+        <v>412550000</v>
       </c>
       <c r="D5" t="n">
-        <v>75172000</v>
+        <v>77325000</v>
       </c>
       <c r="E5" t="n">
-        <v>77650000</v>
+        <v>81470000</v>
       </c>
       <c r="F5" t="n">
-        <v>316206000</v>
+        <v>251449000</v>
       </c>
       <c r="G5" t="n">
-        <v>393856000</v>
+        <v>332919000</v>
       </c>
       <c r="H5" t="n">
-        <v>215237000</v>
+        <v>193396000</v>
       </c>
       <c r="I5" t="n">
-        <v>316206000</v>
+        <v>251449000</v>
       </c>
       <c r="J5" t="n">
-        <v>316206000</v>
+        <v>251449000</v>
       </c>
       <c r="K5" t="n">
-        <v>316206000</v>
+        <v>251449000</v>
       </c>
       <c r="L5" t="n">
-        <v>316206000</v>
+        <v>251449000</v>
       </c>
       <c r="M5" t="n">
-        <v>316206000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+        <v>251449000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5947000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-54867000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>177394000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>7833000</v>
+        <v>10818000</v>
       </c>
       <c r="R5" t="n">
-        <v>7833000</v>
+        <v>10818000</v>
       </c>
       <c r="S5" t="n">
-        <v>134226000</v>
+        <v>148128000</v>
       </c>
       <c r="T5" t="n">
-        <v>364000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>364000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>133862000</v>
+        <v>148128000</v>
       </c>
       <c r="W5" t="n">
-        <v>77650000</v>
+        <v>81470000</v>
       </c>
       <c r="X5" t="n">
-        <v>77650000</v>
+        <v>81470000</v>
       </c>
       <c r="Y5" t="n">
-        <v>51002000</v>
+        <v>56249000</v>
       </c>
       <c r="Z5" t="n">
-        <v>24425000</v>
+        <v>2186000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1096000</v>
+        <v>2665000</v>
       </c>
       <c r="AB5" t="n">
-        <v>25481000</v>
+        <v>51398000</v>
       </c>
       <c r="AC5" t="n">
-        <v>450432000</v>
+        <v>399577000</v>
       </c>
       <c r="AD5" t="n">
-        <v>101333000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>6710000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
+        <v>58053000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>84623000</v>
+        <v>58053000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-92123000</v>
+        <v>-73565000</v>
       </c>
       <c r="AM5" t="n">
-        <v>176746000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>446000</v>
-      </c>
+        <v>131618000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>29319000</v>
+        <v>33047000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>122804000</v>
+        <v>86521000</v>
       </c>
       <c r="AR5" t="n">
-        <v>24177000</v>
+        <v>12050000</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>349099000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>341524000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>22843000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>33150000</v>
+        <v>30321000</v>
       </c>
       <c r="AW5" t="n">
-        <v>127580000</v>
+        <v>135648000</v>
       </c>
       <c r="AX5" t="n">
-        <v>22173000</v>
+        <v>12150000</v>
       </c>
       <c r="AY5" t="n">
-        <v>8151000</v>
+        <v>6291000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>97256000</v>
+        <v>117207000</v>
       </c>
       <c r="BA5" t="n">
-        <v>4612000</v>
+        <v>15874000</v>
       </c>
       <c r="BB5" t="n">
-        <v>8132000</v>
+        <v>12110000</v>
       </c>
       <c r="BC5" t="n">
-        <v>118599000</v>
+        <v>114156000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-2060000</v>
+        <v>-41837000</v>
       </c>
       <c r="BE5" t="n">
-        <v>120659000</v>
+        <v>155993000</v>
       </c>
       <c r="BF5" t="n">
-        <v>57026000</v>
+        <v>10572000</v>
       </c>
       <c r="BG5" t="n">
-        <v>54548000</v>
+        <v>6427000</v>
       </c>
       <c r="BH5" t="n">
-        <v>2478000</v>
+        <v>4145000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2478000</v>
+        <v>4145000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>412550000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>412550000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>94711000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99120000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>339839000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>197580000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>240719000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5947000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-64983000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>177394000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10818000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10818000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>159282000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>159282000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>99120000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>99120000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>41042000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1182000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2323000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>37537000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>400001000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>43139000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>43139000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-86249000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>129388000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>31353000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>86521000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11514000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>356862000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>17433000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>62753000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>117638000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11491000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6653000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>99494000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>10717000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11385000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>118578000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-10503000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>129081000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>18358000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>13949000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4409000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>4409000</v>
       </c>
     </row>
   </sheetData>
@@ -2260,7 +2440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,584 +2697,639 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-11628000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-101319000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>106390000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>212000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1909000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4145000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13094000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>217000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-9166000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1181000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>-4102000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>212000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>212000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5071000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5071000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-101319000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>106390000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>261000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>-3009000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>-628000</v>
-      </c>
+        <v>500000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-91800000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>92300000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>55000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-170000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>22148000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-22318000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-1897000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1909000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-9719000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1914000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4682000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-483000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-9366000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>9366000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10708000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-20282000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14739000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2974000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>5256000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>5256000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2063000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>73000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>13356000</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>4438000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>197000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-10753000</v>
+        <v>-48209000</v>
       </c>
       <c r="C3" t="n">
-        <v>-68100000</v>
+        <v>-81450000</v>
       </c>
       <c r="D3" t="n">
-        <v>74240000</v>
+        <v>71900000</v>
       </c>
       <c r="E3" t="n">
-        <v>438000</v>
+        <v>38448000</v>
       </c>
       <c r="F3" t="n">
-        <v>-803000</v>
+        <v>-3010000</v>
       </c>
       <c r="G3" t="n">
-        <v>13094000</v>
+        <v>16571000</v>
       </c>
       <c r="H3" t="n">
-        <v>16571000</v>
+        <v>2478000</v>
       </c>
       <c r="I3" t="n">
-        <v>-358000</v>
+        <v>2156000</v>
       </c>
       <c r="J3" t="n">
-        <v>-3119000</v>
+        <v>11937000</v>
       </c>
       <c r="K3" t="n">
-        <v>3533000</v>
+        <v>24944000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-3045000</v>
+        <v>-3954000</v>
       </c>
       <c r="N3" t="n">
-        <v>438000</v>
+        <v>38448000</v>
       </c>
       <c r="O3" t="n">
-        <v>438000</v>
+        <v>38448000</v>
       </c>
       <c r="P3" t="n">
-        <v>6140000</v>
+        <v>-9550000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6140000</v>
+        <v>-9550000</v>
       </c>
       <c r="R3" t="n">
-        <v>-68100000</v>
+        <v>-81450000</v>
       </c>
       <c r="S3" t="n">
-        <v>74240000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>850000</v>
-      </c>
+        <v>71900000</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>3298000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>32192000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-21528000</v>
+      </c>
       <c r="Y3" t="n">
-        <v>1308000</v>
+        <v>4797000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1534000</v>
+        <v>34507000</v>
       </c>
       <c r="AA3" t="n">
-        <v>39489000</v>
+        <v>72576000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-37955000</v>
+        <v>-38069000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>29843000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>29843000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-803000</v>
+        <v>-2984000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-803000</v>
+        <v>-3010000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-9950000</v>
+        <v>-45199000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-727000</v>
+        <v>-4404000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8257000</v>
+        <v>-34045000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-3782000</v>
+        <v>-2837000</v>
       </c>
       <c r="AL3" t="n">
-        <v>15622000</v>
+        <v>29297000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-15264000</v>
+        <v>37161000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13585000</v>
+        <v>-38280000</v>
       </c>
       <c r="AO3" t="n">
-        <v>16903000</v>
+        <v>-8119000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-18807000</v>
+        <v>-51267000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>688000</v>
+        <v>-1260000</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>4419000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5076000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>5344000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>5076000</v>
+        <v>5344000</v>
       </c>
       <c r="AV3" t="n">
-        <v>382000</v>
+        <v>4863000</v>
       </c>
       <c r="AW3" t="n">
-        <v>383000</v>
+        <v>327000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>-5056000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-92705000</v>
+        <v>-24641000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-48209000</v>
+        <v>-10753000</v>
       </c>
       <c r="C4" t="n">
-        <v>-81450000</v>
+        <v>-68100000</v>
       </c>
       <c r="D4" t="n">
-        <v>71900000</v>
+        <v>74240000</v>
       </c>
       <c r="E4" t="n">
-        <v>38448000</v>
+        <v>438000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3010000</v>
+        <v>-803000</v>
       </c>
       <c r="G4" t="n">
+        <v>13094000</v>
+      </c>
+      <c r="H4" t="n">
         <v>16571000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2478000</v>
-      </c>
       <c r="I4" t="n">
-        <v>2156000</v>
+        <v>-358000</v>
       </c>
       <c r="J4" t="n">
-        <v>11937000</v>
+        <v>-3119000</v>
       </c>
       <c r="K4" t="n">
-        <v>24944000</v>
+        <v>3533000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-3954000</v>
+        <v>-3045000</v>
       </c>
       <c r="N4" t="n">
-        <v>38448000</v>
+        <v>438000</v>
       </c>
       <c r="O4" t="n">
-        <v>38448000</v>
+        <v>438000</v>
       </c>
       <c r="P4" t="n">
-        <v>-9550000</v>
+        <v>6140000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9550000</v>
+        <v>6140000</v>
       </c>
       <c r="R4" t="n">
-        <v>-81450000</v>
+        <v>-68100000</v>
       </c>
       <c r="S4" t="n">
-        <v>71900000</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
+        <v>74240000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>850000</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>32192000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-21528000</v>
-      </c>
+        <v>3298000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>4797000</v>
+        <v>1308000</v>
       </c>
       <c r="Z4" t="n">
-        <v>34507000</v>
+        <v>1534000</v>
       </c>
       <c r="AA4" t="n">
-        <v>72576000</v>
+        <v>39489000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-38069000</v>
+        <v>-37955000</v>
       </c>
       <c r="AC4" t="n">
-        <v>29843000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>29843000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2984000</v>
+        <v>-803000</v>
       </c>
       <c r="AF4" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3010000</v>
+        <v>-803000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-45199000</v>
+        <v>-9950000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4404000</v>
+        <v>-727000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-34045000</v>
+        <v>8257000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2837000</v>
+        <v>-3782000</v>
       </c>
       <c r="AL4" t="n">
-        <v>29297000</v>
+        <v>15622000</v>
       </c>
       <c r="AM4" t="n">
-        <v>37161000</v>
+        <v>-15264000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-38280000</v>
+        <v>13585000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-8119000</v>
+        <v>16903000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-51267000</v>
+        <v>-18807000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1260000</v>
+        <v>688000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4419000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>5344000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>5076000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>5344000</v>
+        <v>5076000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4863000</v>
+        <v>382000</v>
       </c>
       <c r="AW4" t="n">
-        <v>327000</v>
+        <v>383000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-5056000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>-24641000</v>
+        <v>-92705000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-64737000</v>
+        <v>-11628000</v>
       </c>
       <c r="C5" t="n">
-        <v>-91800000</v>
+        <v>-101319000</v>
       </c>
       <c r="D5" t="n">
-        <v>92300000</v>
+        <v>106390000</v>
       </c>
       <c r="E5" t="n">
-        <v>12709000</v>
+        <v>212000</v>
       </c>
       <c r="F5" t="n">
-        <v>-964000</v>
+        <v>-1909000</v>
       </c>
       <c r="G5" t="n">
-        <v>2478000</v>
+        <v>4145000</v>
       </c>
       <c r="H5" t="n">
-        <v>58319000</v>
+        <v>13094000</v>
       </c>
       <c r="I5" t="n">
-        <v>827000</v>
+        <v>217000</v>
       </c>
       <c r="J5" t="n">
-        <v>-56668000</v>
+        <v>-9166000</v>
       </c>
       <c r="K5" t="n">
-        <v>9348000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>261000</v>
-      </c>
+        <v>1181000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-3861000</v>
+        <v>-4102000</v>
       </c>
       <c r="N5" t="n">
-        <v>12709000</v>
+        <v>212000</v>
       </c>
       <c r="O5" t="n">
-        <v>12709000</v>
+        <v>212000</v>
       </c>
       <c r="P5" t="n">
-        <v>500000</v>
+        <v>5071000</v>
       </c>
       <c r="Q5" t="n">
-        <v>500000</v>
+        <v>5071000</v>
       </c>
       <c r="R5" t="n">
-        <v>-91800000</v>
+        <v>-101319000</v>
       </c>
       <c r="S5" t="n">
-        <v>92300000</v>
+        <v>106390000</v>
       </c>
       <c r="T5" t="n">
-        <v>500000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-91800000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>92300000</v>
-      </c>
+        <v>-3009000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-2243000</v>
+        <v>-628000</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>766000</v>
+        <v>55000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2073000</v>
+        <v>-170000</v>
       </c>
       <c r="AA5" t="n">
-        <v>13979000</v>
+        <v>22148000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-16052000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>-22318000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-936000</v>
+        <v>-1897000</v>
       </c>
       <c r="AF5" t="n">
-        <v>28000</v>
+        <v>12000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-964000</v>
+        <v>-1909000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-63773000</v>
+        <v>-9719000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1574000</v>
+        <v>-1914000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24024000</v>
+        <v>4142000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-4742000</v>
+        <v>-483000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-398000</v>
+        <v>-9366000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-29874000</v>
+        <v>9366000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-2008000</v>
+        <v>10708000</v>
       </c>
       <c r="AO5" t="n">
-        <v>132165000</v>
+        <v>-20822000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-71119000</v>
+        <v>14739000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10632000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4438000</v>
-      </c>
+        <v>2974000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>6542000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>197000</v>
-      </c>
+        <v>5256000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>6345000</v>
+        <v>5256000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1196000</v>
+        <v>2063000</v>
       </c>
       <c r="AW5" t="n">
-        <v>835000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
+        <v>73000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>-125182000</v>
+        <v>13356000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-22047000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-98097000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>113070000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1273000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4409000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4145000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-61000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>325000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11658000</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-3609000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>294000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14973000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14973000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-98097000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>113070000</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>9441000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>540000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5410000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>22843000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-17433000</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-1273000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-1273000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-20774000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-2023000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11454000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7724000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-11184000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-29988000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>18010000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>26912000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2157000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>5345000</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>5345000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-7996000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>734000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>-8435000</v>
       </c>
     </row>
   </sheetData>
@@ -3619,197 +3854,197 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3894,7 +4129,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Wenji  Huang', 'age': 56, 'title': 'Founder, CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 376396, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guang  Yang', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 349759, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhenshuang  Lin', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 385661, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kin Hung  Chung', 'age': 59, 'title': 'Executive Director', 'yearBorn': 1966, 'fiscalYear': 2024, 'totalPay': 192252, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Steven Andrew  Chen', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Keung  Yuen', 'age': 43, 'title': 'Company Secretary', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Wenji  Huang', 'age': 56, 'title': 'Founder, CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 376434, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guang  Yang', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2024, 'totalPay': 349794, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhenshuang  Lin', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2024, 'totalPay': 385700, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kin Hung  Chung', 'age': 59, 'title': 'Executive Director', 'yearBorn': 1966, 'fiscalYear': 2024, 'totalPay': 192271, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Steven Andrew  Chen', 'age': 57, 'title': 'Executive Chairman', 'yearBorn': 1968, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wai Keung  Yuen', 'age': 43, 'title': 'Company Secretary', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3912,55 +4147,55 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V2" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="W2" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="X2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.343</v>
+        <v>-2.317</v>
       </c>
       <c r="AE2" t="n">
-        <v>22500</v>
+        <v>50000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22500</v>
+        <v>50000</v>
       </c>
       <c r="AG2" t="n">
-        <v>33351</v>
+        <v>39500</v>
       </c>
       <c r="AH2" t="n">
-        <v>38537</v>
+        <v>82343</v>
       </c>
       <c r="AI2" t="n">
-        <v>38537</v>
+        <v>82343</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3969,13 +4204,13 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1093981056</v>
+        <v>1206719616</v>
       </c>
       <c r="AO2" t="n">
-        <v>1093981000</v>
+        <v>1206719500</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AQ2" t="n">
         <v>5</v>
@@ -3987,13 +4222,13 @@
         <v>0.14</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.9562457</v>
+        <v>4.3639507</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.8642</v>
+        <v>2.785</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.01965</v>
+        <v>3.12115</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4010,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1161643008</v>
+        <v>1260654976</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.03658</v>
@@ -4031,10 +4266,10 @@
         <v>417550000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.67519665</v>
+        <v>0.674161</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.8803508</v>
+        <v>4.28681</v>
       </c>
       <c r="BJ2" t="n">
         <v>1767139200</v>
@@ -4060,16 +4295,16 @@
         <v>1593993600</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.201</v>
+        <v>4.559</v>
       </c>
       <c r="BR2" t="n">
-        <v>355.134</v>
+        <v>385.404</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.701031</v>
+        <v>1.8058252</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -4077,7 +4312,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4176,150 +4411,150 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CX2" t="n">
+        <v>-0.34482723</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.00999999</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>2.73 - 2.89</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>39500</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>2.1413043</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>0.92 - 5.0</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>180.58252</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1743162440</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1743162440</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.10500002</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.03770198</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.23114991</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.07405921</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>China Jicheng Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>1781769467</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Asia Strategy Digit Technology Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>finmb_274637329</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1423791000000</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>ASIA STRAT TECH</t>
         </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>1780379606</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>finmb_274637329</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Asia Strategy Digit Technology Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>2.62 - 2.62</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>33351</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1.7199999</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1.9111111</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>0.9 - 5.0</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.476</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>170.1031</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1743162440</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1743162440</v>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.24420023</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.08525948999999999</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.3996501</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.1323498</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>China Jicheng Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1423791000000</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
